--- a/data/trans_bre/P6902-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6902-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 33,34</t>
+          <t>-15,91; 36,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-42,57; 37,28</t>
+          <t>-48,61; 40,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 68,04</t>
+          <t>-6,96; 67,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 93,71</t>
+          <t>-19,76; 99,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 118,68</t>
+          <t>-32,11; 144,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 90,57</t>
+          <t>-57,63; 93,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 439,73</t>
+          <t>-18,15; 437,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-23,03; —</t>
+          <t>-23,11; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 27,66</t>
+          <t>-0,59; 26,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 18,71</t>
+          <t>-16,0; 17,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 41,43</t>
+          <t>3,82; 39,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 17,16</t>
+          <t>-21,19; 16,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 71,84</t>
+          <t>-1,25; 72,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 42,02</t>
+          <t>-26,09; 39,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,06; 151,12</t>
+          <t>11,82; 138,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 26,69</t>
+          <t>-26,54; 26,21</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 19,31</t>
+          <t>-11,27; 18,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 28,57</t>
+          <t>-2,01; 29,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,18; 37,9</t>
+          <t>9,07; 38,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 20,66</t>
+          <t>-6,83; 20,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,52; 52,44</t>
+          <t>-21,73; 45,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 72,52</t>
+          <t>-3,93; 77,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,05; 122,59</t>
+          <t>19,95; 129,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 44,52</t>
+          <t>-11,44; 44,47</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 21,31</t>
+          <t>-14,39; 22,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 30,85</t>
+          <t>-7,19; 30,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 23,53</t>
+          <t>-13,3; 22,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,94; 8,45</t>
+          <t>-39,13; 9,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 53,55</t>
+          <t>-27,86; 57,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 101,51</t>
+          <t>-15,6; 101,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 58,45</t>
+          <t>-23,15; 51,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,01; 13,45</t>
+          <t>-58,68; 15,07</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 34,44</t>
+          <t>-19,53; 37,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 42,95</t>
+          <t>-9,21; 41,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 32,49</t>
+          <t>-17,86; 30,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 18,02</t>
+          <t>-11,67; 16,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-65,36; 162,11</t>
+          <t>-56,44; 174,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 129,14</t>
+          <t>-12,67; 123,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,88; 73,75</t>
+          <t>-28,25; 74,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 35,19</t>
+          <t>-16,69; 28,75</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 84,17</t>
+          <t>-35,59; 83,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 17,13</t>
+          <t>-0,27; 15,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 19,07</t>
+          <t>2,11; 19,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,18; 26,25</t>
+          <t>9,03; 26,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 8,58</t>
+          <t>-19,44; 7,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 43,04</t>
+          <t>-0,43; 39,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 44,65</t>
+          <t>4,33; 45,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,1; 65,36</t>
+          <t>19,68; 65,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 14,38</t>
+          <t>-30,44; 13,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6902-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6902-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34,92</t>
+          <t>51,22</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>147,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 36,3</t>
+          <t>-17,3; 37,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-48,61; 40,01</t>
+          <t>-51,54; 33,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 67,46</t>
+          <t>-9,77; 64,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 99,23</t>
+          <t>-17,1; 92,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 144,37</t>
+          <t>-35,94; 135,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,63; 93,77</t>
+          <t>-62,91; 76,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 437,0</t>
+          <t>-24,36; 430,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-23,11; —</t>
+          <t>-20,07; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,41</t>
+          <t>-7,3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-4,59%</t>
+          <t>-9,56%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 26,85</t>
+          <t>-0,81; 28,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 17,62</t>
+          <t>-15,55; 18,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 39,26</t>
+          <t>6,18; 42,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 16,69</t>
+          <t>-24,94; 10,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 72,75</t>
+          <t>-2,66; 73,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 39,47</t>
+          <t>-26,19; 41,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 138,9</t>
+          <t>13,65; 148,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 26,21</t>
+          <t>-29,97; 16,01</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,42</t>
+          <t>6,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 18,53</t>
+          <t>-11,28; 17,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 29,67</t>
+          <t>-2,82; 29,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,07; 38,97</t>
+          <t>9,25; 38,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 20,52</t>
+          <t>-6,96; 19,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 45,47</t>
+          <t>-22,08; 43,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 77,39</t>
+          <t>-5,32; 74,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,95; 129,47</t>
+          <t>19,34; 127,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 44,47</t>
+          <t>-11,84; 42,68</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-10,06</t>
+          <t>8,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-16,06%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 22,57</t>
+          <t>-17,0; 21,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 30,71</t>
+          <t>-3,99; 33,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 22,21</t>
+          <t>-13,18; 21,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,13; 9,3</t>
+          <t>-3,51; 19,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 57,12</t>
+          <t>-31,06; 53,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 101,53</t>
+          <t>-10,81; 106,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 51,34</t>
+          <t>-21,91; 51,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,68; 15,07</t>
+          <t>-4,49; 37,66</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 37,35</t>
+          <t>-20,2; 36,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 41,1</t>
+          <t>-9,45; 41,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 30,85</t>
+          <t>-16,34; 34,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 16,38</t>
+          <t>-11,98; 16,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-56,44; 174,4</t>
+          <t>-58,53; 161,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 123,32</t>
+          <t>-19,56; 121,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 74,7</t>
+          <t>-24,78; 77,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 28,75</t>
+          <t>-16,36; 28,12</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40,31</t>
+          <t>41,95</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>158,78%</t>
+          <t>176,11%</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 83,52</t>
+          <t>-18,39; 83,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-2,16%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 15,65</t>
+          <t>-0,25; 15,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,11; 19,13</t>
+          <t>1,2; 18,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,03; 26,24</t>
+          <t>8,58; 25,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 7,81</t>
+          <t>-1,52; 12,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 39,4</t>
+          <t>-0,4; 39,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,33; 45,6</t>
+          <t>2,74; 44,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,68; 65,5</t>
+          <t>18,79; 64,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 13,13</t>
+          <t>-2,22; 23,04</t>
         </is>
       </c>
     </row>
